--- a/public/excel_template/상품 등록 템플릿.xlsx
+++ b/public/excel_template/상품 등록 템플릿.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="9180" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="사용법" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>`Sheet1`에 등록 또는 수정하고자 하는 상품들을 작성합니다.</t>
   </si>
@@ -86,42 +86,6 @@
   </si>
   <si>
     <t>D</t>
-  </si>
-  <si>
-    <t>주식회사 다우기술</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>테스트 상품</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>발행당</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.epopkon.com/Resource/images/goods/EP0000806907/goods_img5.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반쿠폰</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -563,51 +527,10 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2">
-        <v>100</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
+      <c r="N2" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -686,35 +609,35 @@
       </c>
       <c r="E2" t="str">
         <f>IF(Sheet1!E2="","",Sheet1!E2)</f>
-        <v>테스트 상품</v>
-      </c>
-      <c r="F2">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <f>IF(Sheet1!F2="","",Sheet1!F2)</f>
-        <v>1</v>
-      </c>
-      <c r="G2">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <f>IF(Sheet1!G2="","",Sheet1!G2)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <f>IF(COUNTIF(상품군!$A:$A, UPPER(Sheet1!H2)) &gt; 0, UPPER(Sheet1!H2), "")</f>
-        <v>A</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <f>IF(Sheet1!I2="","",Sheet1!I2)</f>
-        <v>일반쿠폰</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <f>IF(Sheet1!J2="","",Sheet1!J2)</f>
-        <v>사용</v>
+        <v/>
       </c>
       <c r="K2" t="str">
         <f>IF(Sheet1!K2="","",Sheet1!K2)</f>
-        <v>발행당</v>
-      </c>
-      <c r="L2">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <f>IF(Sheet1!L2="","",Sheet1!L2)</f>
-        <v>100</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <f>IF(Sheet1!M2="","",Sheet1!M2)</f>
@@ -722,11 +645,11 @@
       </c>
       <c r="N2" t="str">
         <f>IF(Sheet1!N2="","",Sheet1!N2)</f>
-        <v>https://www.epopkon.com/Resource/images/goods/EP0000806907/goods_img5.jpg</v>
+        <v/>
       </c>
       <c r="O2" t="str">
         <f>IF(Sheet1!O2="","",Sheet1!O2)</f>
-        <v>테스트 상품</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
